--- a/data/results/2026-2027/Computer-Networks/Computer-Networks-Results.xlsx
+++ b/data/results/2026-2027/Computer-Networks/Computer-Networks-Results.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Exam Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Exam Summary" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,625 +398,1364 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AF12"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="24.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
-    <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="16.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="26.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
+    <col min="13" max="13" width="24.83203125" customWidth="1"/>
+    <col min="14" max="14" width="26.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="30.83203125" customWidth="1"/>
+    <col min="18" max="18" width="16.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
     <col min="20" max="20" width="14.83203125" customWidth="1"/>
     <col min="21" max="21" width="14.83203125" customWidth="1"/>
     <col min="22" max="22" width="14.83203125" customWidth="1"/>
-    <col min="23" max="23" width="18.83203125" customWidth="1"/>
-    <col min="24" max="24" width="16.83203125" customWidth="1"/>
-    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="10.83203125" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
+    <col min="27" max="27" width="12.83203125" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" customWidth="1"/>
+    <col min="29" max="29" width="14.83203125" customWidth="1"/>
+    <col min="30" max="30" width="16.83203125" customWidth="1"/>
+    <col min="31" max="31" width="18.83203125" customWidth="1"/>
+    <col min="32" max="32" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Student Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Registration Number</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Subject Paper</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Total Questions</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Correct Answers</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Wrong Answers</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Marks Obtained</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Evaluation Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Fullscreen Exits</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Tab Switches / Focus Loss</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Total Security Violations</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Timestamp</v>
+      </c>
+      <c r="N1" t="str">
         <v>Student ID</v>
       </c>
-      <c r="B1" t="str">
-        <v>Student Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Registration Number</v>
-      </c>
-      <c r="D1" t="str">
+      <c r="O1" t="str">
         <v>Year</v>
       </c>
-      <c r="E1" t="str">
+      <c r="P1" t="str">
         <v>Section</v>
       </c>
-      <c r="F1" t="str">
-        <v>Subject</v>
-      </c>
-      <c r="G1" t="str">
+      <c r="Q1" t="str">
         <v>Exam Name</v>
       </c>
-      <c r="H1" t="str">
+      <c r="R1" t="str">
+        <v>Exam ID</v>
+      </c>
+      <c r="S1" t="str">
         <v>Exam Date</v>
       </c>
-      <c r="I1" t="str">
+      <c r="T1" t="str">
         <v>Start Time</v>
       </c>
-      <c r="J1" t="str">
-        <v>Submission Time</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Total Questions</v>
-      </c>
-      <c r="L1" t="str">
+      <c r="U1" t="str">
+        <v>Duration</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Time Taken</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Easy Qs</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Medium Qs</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Hard Qs</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Hints Used</v>
+      </c>
+      <c r="AA1" t="str">
         <v>Attempted</v>
       </c>
-      <c r="M1" t="str">
+      <c r="AB1" t="str">
         <v>Unanswered</v>
       </c>
-      <c r="N1" t="str">
-        <v>Correct</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Wrong</v>
-      </c>
-      <c r="P1" t="str">
+      <c r="AC1" t="str">
         <v>Total Marks</v>
       </c>
-      <c r="Q1" t="str">
-        <v>Marks Obtained</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Percentage</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Result</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Duration</v>
-      </c>
-      <c r="U1" t="str">
-        <v>Time Taken</v>
-      </c>
-      <c r="V1" t="str">
-        <v>Tab Switches</v>
-      </c>
-      <c r="W1" t="str">
-        <v>Fullscreen Exits</v>
-      </c>
-      <c r="X1" t="str">
+      <c r="AD1" t="str">
         <v>Auto Submitted</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AE1" t="str">
         <v>Submission Type</v>
       </c>
-      <c r="Z1" t="str">
-        <v>Easy Qs</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>Medium Qs</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>Hard Qs</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>Hints Used</v>
+      <c r="AF1" t="str">
+        <v>Sync Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>6a92dc0e0ec2a2811125f7ae</v>
+        <v>Kalyan</v>
       </c>
       <c r="B2" t="str">
-        <v>A. Sai Ram</v>
+        <v>23A91A0501</v>
       </c>
       <c r="C2" t="str">
-        <v>24HP1A0501</v>
-      </c>
-      <c r="D2" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2" t="str">
+        <v>7 / 20</v>
+      </c>
+      <c r="H2" t="str">
+        <v>35%</v>
+      </c>
+      <c r="I2" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="str">
+        <v>12/8/2026, 9:08:31 am</v>
+      </c>
+      <c r="N2" t="str">
+        <v>6a7beab7e4de8f9d6bef2229</v>
+      </c>
+      <c r="O2" t="str">
         <v>III B.Tech</v>
       </c>
-      <c r="E2" t="str">
+      <c r="P2" t="str">
         <v>A</v>
       </c>
-      <c r="F2" t="str">
-        <v>Computer Networks</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Mid-Term Computer Networks Exam</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2026-08-29</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="Q2" t="str">
+        <v>Computer Networks Mid Examination</v>
+      </c>
+      <c r="R2" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S2" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T2" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J2" t="str">
-        <v>29/8/2026, 6:48:06 pm</v>
-      </c>
-      <c r="K2">
-        <v>50</v>
-      </c>
-      <c r="L2">
+      <c r="U2" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V2" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <v>20</v>
       </c>
-      <c r="M2">
-        <v>30</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>45</v>
-      </c>
-      <c r="P2">
-        <v>50</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>5 / 50</v>
-      </c>
-      <c r="R2" t="str">
-        <v>10%</v>
-      </c>
-      <c r="S2" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="T2" t="str">
-        <v>30 Mins</v>
-      </c>
-      <c r="U2" t="str">
-        <v>18 Mins</v>
-      </c>
-      <c r="V2">
-        <v>2</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2" t="str">
+      <c r="AD2" t="str">
         <v>No</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="AE2" t="str">
         <v>MANUAL</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>Synced</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>6a92dcaa0ec2a2811125faec</v>
+        <v>Kalyan</v>
       </c>
       <c r="B3" t="str">
-        <v>Kalyan</v>
+        <v>23A91A0501</v>
       </c>
       <c r="C3" t="str">
-        <v>24HP1A0541</v>
-      </c>
-      <c r="D3" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3" t="str">
+        <v>8 / 20</v>
+      </c>
+      <c r="H3" t="str">
+        <v>40%</v>
+      </c>
+      <c r="I3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="str">
+        <v>12/8/2026, 9:23:36 am</v>
+      </c>
+      <c r="N3" t="str">
+        <v>6a7bee4026a138a9bc81597f</v>
+      </c>
+      <c r="O3" t="str">
         <v>III B.Tech</v>
       </c>
-      <c r="E3" t="str">
+      <c r="P3" t="str">
         <v>A</v>
       </c>
-      <c r="F3" t="str">
-        <v>Computer Networks</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="Q3" t="str">
         <v>Computer Networks Mid Examination</v>
       </c>
-      <c r="H3" t="str">
-        <v>2026-08-29</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="R3" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S3" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T3" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J3" t="str">
-        <v>29/8/2026, 6:50:42 pm</v>
-      </c>
-      <c r="K3">
-        <v>50</v>
-      </c>
-      <c r="L3">
+      <c r="U3" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V3" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
         <v>20</v>
       </c>
-      <c r="M3">
-        <v>30</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>50</v>
-      </c>
-      <c r="P3">
-        <v>50</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>0 / 50</v>
-      </c>
-      <c r="R3" t="str">
-        <v>0%</v>
-      </c>
-      <c r="S3" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="T3" t="str">
-        <v>30 Mins</v>
-      </c>
-      <c r="U3" t="str">
-        <v>20 Mins</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3" t="str">
+      <c r="AD3" t="str">
         <v>No</v>
       </c>
-      <c r="Y3" t="str">
+      <c r="AE3" t="str">
         <v>MANUAL</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Synced</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6a96db1597949d929ea922ea</v>
+        <v>S. Dinesh</v>
       </c>
       <c r="B4" t="str">
-        <v>Test Student</v>
+        <v>24HPA10654</v>
       </c>
       <c r="C4" t="str">
-        <v>TEST_RUNNER_1434</v>
-      </c>
-      <c r="D4" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D4">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>14</v>
+      </c>
+      <c r="G4" t="str">
+        <v>6 / 20</v>
+      </c>
+      <c r="H4" t="str">
+        <v>30%</v>
+      </c>
+      <c r="I4" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="str">
+        <v>12/8/2026, 9:30:27 am</v>
+      </c>
+      <c r="N4" t="str">
+        <v>6a7befdbf172021f8b9c8223</v>
+      </c>
+      <c r="O4" t="str">
         <v>III B.Tech</v>
       </c>
-      <c r="E4" t="str">
+      <c r="P4" t="str">
         <v>A</v>
       </c>
-      <c r="F4" t="str">
-        <v>Computer Networks</v>
-      </c>
-      <c r="G4" t="str">
+      <c r="Q4" t="str">
         <v>Computer Networks Mid Examination</v>
       </c>
-      <c r="H4" t="str">
-        <v>2026-09-01</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="R4" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S4" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T4" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J4" t="str">
-        <v>1/9/2026, 7:33:01 pm</v>
-      </c>
-      <c r="K4">
-        <v>50</v>
-      </c>
-      <c r="L4">
-        <v>9</v>
-      </c>
-      <c r="M4">
-        <v>41</v>
-      </c>
-      <c r="N4">
-        <v>5</v>
-      </c>
-      <c r="O4">
-        <v>45</v>
-      </c>
-      <c r="P4">
-        <v>50</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>5 / 50</v>
-      </c>
-      <c r="R4" t="str">
-        <v>10%</v>
-      </c>
-      <c r="S4" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="T4" t="str">
+      <c r="U4" t="str">
         <v>30 Mins</v>
       </c>
-      <c r="U4" t="str">
+      <c r="V4" t="str">
         <v>20 Mins</v>
       </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
       <c r="W4">
         <v>0</v>
       </c>
-      <c r="X4" t="str">
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>20</v>
+      </c>
+      <c r="AD4" t="str">
         <v>No</v>
       </c>
-      <c r="Y4" t="str">
+      <c r="AE4" t="str">
         <v>MANUAL</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>Synced</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>6a96dbd3607a4be5832cacbf</v>
+        <v>Kalyan</v>
       </c>
       <c r="B5" t="str">
-        <v>Test Student</v>
+        <v>23A91A0501</v>
       </c>
       <c r="C5" t="str">
-        <v>TEST_RUNNER_1528</v>
-      </c>
-      <c r="D5" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5" t="str">
+        <v>3 / 20</v>
+      </c>
+      <c r="H5" t="str">
+        <v>15%</v>
+      </c>
+      <c r="I5" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <v>12/8/2026, 9:39:51 am</v>
+      </c>
+      <c r="N5" t="str">
+        <v>6a7bf20fb8e0919270ba213a</v>
+      </c>
+      <c r="O5" t="str">
         <v>III B.Tech</v>
       </c>
-      <c r="E5" t="str">
+      <c r="P5" t="str">
         <v>A</v>
       </c>
-      <c r="F5" t="str">
-        <v>Computer Networks</v>
-      </c>
-      <c r="G5" t="str">
+      <c r="Q5" t="str">
         <v>Computer Networks Mid Examination</v>
       </c>
-      <c r="H5" t="str">
-        <v>2026-09-01</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="R5" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S5" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T5" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J5" t="str">
-        <v>1/9/2026, 7:36:11 pm</v>
-      </c>
-      <c r="K5">
-        <v>10</v>
-      </c>
-      <c r="L5">
-        <v>9</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>6</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-      <c r="P5">
-        <v>16</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>7 / 16</v>
-      </c>
-      <c r="R5" t="str">
-        <v>44%</v>
-      </c>
-      <c r="S5" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="T5" t="str">
+      <c r="U5" t="str">
         <v>30 Mins</v>
       </c>
-      <c r="U5" t="str">
+      <c r="V5" t="str">
         <v>20 Mins</v>
       </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
       <c r="W5">
         <v>0</v>
       </c>
-      <c r="X5" t="str">
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="str">
         <v>No</v>
       </c>
-      <c r="Y5" t="str">
+      <c r="AE5" t="str">
         <v>MANUAL</v>
       </c>
-      <c r="Z5">
-        <v>4</v>
-      </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>3</v>
-      </c>
-      <c r="AC5">
-        <v>3</v>
+      <c r="AF5" t="str">
+        <v>Synced</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6a96dbf06320d726590f6118</v>
+        <v>A. Sai Ram</v>
       </c>
       <c r="B6" t="str">
-        <v>Test Student</v>
+        <v>24HP1A0501</v>
       </c>
       <c r="C6" t="str">
-        <v>TEST_RUNNER_0732</v>
-      </c>
-      <c r="D6" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>45</v>
+      </c>
+      <c r="G6" t="str">
+        <v>5 / 50</v>
+      </c>
+      <c r="H6" t="str">
+        <v>10%</v>
+      </c>
+      <c r="I6" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6" t="str">
+        <v>29/8/2026, 6:48:06 pm</v>
+      </c>
+      <c r="N6" t="str">
+        <v>6a92dc0e0ec2a2811125f7ae</v>
+      </c>
+      <c r="O6" t="str">
         <v>III B.Tech</v>
       </c>
-      <c r="E6" t="str">
+      <c r="P6" t="str">
         <v>A</v>
       </c>
-      <c r="F6" t="str">
-        <v>Computer Networks</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Computer Networks Mid Examination</v>
-      </c>
-      <c r="H6" t="str">
-        <v>2026-09-01</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="Q6" t="str">
+        <v>Mid-Term Computer Networks Exam</v>
+      </c>
+      <c r="R6" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S6" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="T6" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J6" t="str">
-        <v>1/9/2026, 7:36:40 pm</v>
-      </c>
-      <c r="K6">
-        <v>10</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>6</v>
-      </c>
-      <c r="O6">
-        <v>4</v>
-      </c>
-      <c r="P6">
-        <v>17</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>7 / 17</v>
-      </c>
-      <c r="R6" t="str">
-        <v>41%</v>
-      </c>
-      <c r="S6" t="str">
-        <v>PASS</v>
-      </c>
-      <c r="T6" t="str">
+      <c r="U6" t="str">
         <v>30 Mins</v>
       </c>
-      <c r="U6" t="str">
-        <v>20 Mins</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
+      <c r="V6" t="str">
+        <v>18 Mins</v>
       </c>
       <c r="W6">
         <v>0</v>
       </c>
-      <c r="X6" t="str">
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>20</v>
+      </c>
+      <c r="AB6">
+        <v>30</v>
+      </c>
+      <c r="AC6">
+        <v>20</v>
+      </c>
+      <c r="AD6" t="str">
         <v>No</v>
       </c>
-      <c r="Y6" t="str">
+      <c r="AE6" t="str">
         <v>MANUAL</v>
       </c>
-      <c r="Z6">
-        <v>3</v>
-      </c>
-      <c r="AA6">
-        <v>4</v>
-      </c>
-      <c r="AB6">
-        <v>3</v>
-      </c>
-      <c r="AC6">
-        <v>3</v>
+      <c r="AF6" t="str">
+        <v>Synced</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Kalyan</v>
+      </c>
+      <c r="B7" t="str">
+        <v>24HP1A0541</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D7">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7" t="str">
+        <v>0 / 50</v>
+      </c>
+      <c r="H7" t="str">
+        <v>0%</v>
+      </c>
+      <c r="I7" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7" t="str">
+        <v>29/8/2026, 6:50:42 pm</v>
+      </c>
+      <c r="N7" t="str">
+        <v>6a92dcaa0ec2a2811125faec</v>
+      </c>
+      <c r="O7" t="str">
+        <v>III B.Tech</v>
+      </c>
+      <c r="P7" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Computer Networks Mid Examination</v>
+      </c>
+      <c r="R7" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S7" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="T7" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U7" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V7" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>20</v>
+      </c>
+      <c r="AB7">
+        <v>30</v>
+      </c>
+      <c r="AC7">
+        <v>20</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>No</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>MANUAL</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>Synced</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ADDANKI AMULYA</v>
+      </c>
+      <c r="B8" t="str">
+        <v>24HP1A4401</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D8">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>45</v>
+      </c>
+      <c r="G8" t="str">
+        <v>9 / 83</v>
+      </c>
+      <c r="H8" t="str">
+        <v>11%</v>
+      </c>
+      <c r="I8" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="str">
+        <v>4/9/2026, 8:07:33 pm</v>
+      </c>
+      <c r="N8" t="str">
         <v>6a9ad7add24e76ddd128137c</v>
       </c>
-      <c r="B7" t="str">
-        <v>ADDANKI AMULYA</v>
-      </c>
-      <c r="C7" t="str">
-        <v>24HP1A4401</v>
-      </c>
-      <c r="D7" t="str">
+      <c r="O8" t="str">
         <v>3 Year</v>
       </c>
-      <c r="E7" t="str">
+      <c r="P8" t="str">
         <v>A</v>
       </c>
-      <c r="F7" t="str">
+      <c r="Q8" t="str">
+        <v>Computer Networks Mid Examination</v>
+      </c>
+      <c r="R8" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S8" t="str">
+        <v>2026-09-04</v>
+      </c>
+      <c r="T8" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U8" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V8" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W8">
+        <v>17</v>
+      </c>
+      <c r="X8">
+        <v>17</v>
+      </c>
+      <c r="Y8">
+        <v>16</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>20</v>
+      </c>
+      <c r="AB8">
+        <v>30</v>
+      </c>
+      <c r="AC8">
+        <v>83</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>No</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>MANUAL</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>Synced</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>GUMMADI VENKATA SAI</v>
+      </c>
+      <c r="B9" t="str">
+        <v>24HP1A0565</v>
+      </c>
+      <c r="C9" t="str">
         <v>Computer Networks</v>
       </c>
-      <c r="G7" t="str">
+      <c r="D9">
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>18</v>
+      </c>
+      <c r="G9" t="str">
+        <v>3 / 32</v>
+      </c>
+      <c r="H9" t="str">
+        <v>9%</v>
+      </c>
+      <c r="I9" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="str">
+        <v>6/9/2026, 11:07:08 am</v>
+      </c>
+      <c r="N9" t="str">
+        <v>6a9cfc04cb79561fb8d0552a</v>
+      </c>
+      <c r="O9" t="str">
+        <v>3 Year</v>
+      </c>
+      <c r="P9" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q9" t="str">
         <v>Computer Networks Mid Examination</v>
       </c>
-      <c r="H7" t="str">
-        <v>2026-09-04</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="R9" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+      <c r="S9" t="str">
+        <v>2026-09-06</v>
+      </c>
+      <c r="T9" t="str">
         <v>10:00 AM</v>
       </c>
-      <c r="J7" t="str">
-        <v>4/9/2026, 8:07:33 pm</v>
-      </c>
-      <c r="K7">
+      <c r="U9" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V9" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W9">
+        <v>8</v>
+      </c>
+      <c r="X9">
+        <v>5</v>
+      </c>
+      <c r="Y9">
+        <v>7</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>20</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>32</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>No</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>MANUAL</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>Synced</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SHAIK RESHMI</v>
+      </c>
+      <c r="B10" t="str">
+        <v>24HP1A0588</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D10">
+        <v>20</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10">
+        <v>18</v>
+      </c>
+      <c r="G10" t="str">
+        <v>3 / 35</v>
+      </c>
+      <c r="H10" t="str">
+        <v>9%</v>
+      </c>
+      <c r="I10" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="str">
+        <v>1/10/2026, 6:47:34 pm</v>
+      </c>
+      <c r="N10" t="str">
+        <v>6abe5d6e686f5ba0f3629ecb</v>
+      </c>
+      <c r="O10" t="str">
+        <v>3 Year</v>
+      </c>
+      <c r="P10" t="str">
+        <v>B</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Computer Networks Mid Examination</v>
+      </c>
+      <c r="R10" t="str">
+        <v>EXAM_COMPUTER_NETWORKS</v>
+      </c>
+      <c r="S10" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T10" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U10" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V10" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W10">
+        <v>5</v>
+      </c>
+      <c r="X10">
+        <v>5</v>
+      </c>
+      <c r="Y10">
+        <v>10</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>13</v>
+      </c>
+      <c r="AB10">
+        <v>7</v>
+      </c>
+      <c r="AC10">
+        <v>35</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>No</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>MANUAL</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>Synced</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>KADALI POOJITHA</v>
+      </c>
+      <c r="B11" t="str">
+        <v>24HP1A0586</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11" t="str">
+        <v>5 / 31</v>
+      </c>
+      <c r="H11" t="str">
+        <v>16%</v>
+      </c>
+      <c r="I11" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="str">
+        <v>1/10/2026, 7:08:15 pm</v>
+      </c>
+      <c r="N11" t="str">
+        <v>6abe62478702c81b67f2b33a</v>
+      </c>
+      <c r="O11" t="str">
+        <v>3 Year</v>
+      </c>
+      <c r="P11" t="str">
+        <v>B</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Computer Networks Mid Examination</v>
+      </c>
+      <c r="R11" t="str">
+        <v>EXAM_COMPUTER_NETWORKS</v>
+      </c>
+      <c r="S11" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T11" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U11" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V11" t="str">
+        <v>20 Mins</v>
+      </c>
+      <c r="W11">
+        <v>9</v>
+      </c>
+      <c r="X11">
+        <v>8</v>
+      </c>
+      <c r="Y11">
+        <v>3</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>12</v>
+      </c>
+      <c r="AB11">
+        <v>8</v>
+      </c>
+      <c r="AC11">
+        <v>31</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>No</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>MANUAL</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>Synced</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>JANGAM HRUDAY SAGAR</v>
+      </c>
+      <c r="B12" t="str">
+        <v>24HP1A0544</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Computer Networks</v>
+      </c>
+      <c r="D12">
         <v>50</v>
       </c>
-      <c r="L7">
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>45</v>
+      </c>
+      <c r="G12" t="str">
+        <v>9 / 83</v>
+      </c>
+      <c r="H12" t="str">
+        <v>11%</v>
+      </c>
+      <c r="I12" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="str">
+        <v>1/10/2026, 7:29:08 pm</v>
+      </c>
+      <c r="N12" t="str">
+        <v>6abe672c12e8fbef15a77e46</v>
+      </c>
+      <c r="O12" t="str">
+        <v>3 Year</v>
+      </c>
+      <c r="P12" t="str">
+        <v>A</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Mid-Term Computer Networks Exam</v>
+      </c>
+      <c r="R12" t="str">
+        <v>EXAM_CN_001</v>
+      </c>
+      <c r="S12" t="str">
+        <v>2026-10-01</v>
+      </c>
+      <c r="T12" t="str">
+        <v>10:00 AM</v>
+      </c>
+      <c r="U12" t="str">
+        <v>30 Mins</v>
+      </c>
+      <c r="V12" t="str">
+        <v>15 Mins</v>
+      </c>
+      <c r="W12">
+        <v>17</v>
+      </c>
+      <c r="X12">
+        <v>17</v>
+      </c>
+      <c r="Y12">
+        <v>16</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
         <v>20</v>
       </c>
-      <c r="M7">
+      <c r="AB12">
         <v>30</v>
       </c>
-      <c r="N7">
-        <v>5</v>
-      </c>
-      <c r="O7">
-        <v>45</v>
-      </c>
-      <c r="P7">
+      <c r="AC12">
         <v>83</v>
       </c>
-      <c r="Q7" t="str">
-        <v>9 / 83</v>
-      </c>
-      <c r="R7" t="str">
-        <v>11%</v>
-      </c>
-      <c r="S7" t="str">
-        <v>FAIL</v>
-      </c>
-      <c r="T7" t="str">
-        <v>30 Mins</v>
-      </c>
-      <c r="U7" t="str">
-        <v>20 Mins</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7" t="str">
+      <c r="AD12" t="str">
         <v>No</v>
       </c>
-      <c r="Y7" t="str">
+      <c r="AE12" t="str">
         <v>MANUAL</v>
       </c>
-      <c r="Z7">
-        <v>17</v>
-      </c>
-      <c r="AA7">
-        <v>17</v>
-      </c>
-      <c r="AB7">
-        <v>16</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
+      <c r="AF12" t="str">
+        <v>Synced</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF12"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B16"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Metric / Parameter</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Subject</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Computer Networks</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Exam Name</v>
+      </c>
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Exam ID</v>
+      </c>
+      <c r="B4" t="str">
+        <v>EXAM_GEN_001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Exam Date</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-10-01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Total Submissions</v>
+      </c>
+      <c r="B6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Passed Students Count</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Failed Students Count</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Pass Percentage</v>
+      </c>
+      <c r="B9" t="str">
+        <v>9%</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Average Percentage</v>
+      </c>
+      <c r="B10" t="str">
+        <v>17%</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Highest Marks Obtained</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Lowest Marks Obtained</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Total Tab Switches Logged</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Total Fullscreen Exits Logged</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Auto-Submitted Exams Count</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Summary Generated At</v>
+      </c>
+      <c r="B16" t="str">
+        <v>1/10/2026, 7:30:45 pm</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B16"/>
   </ignoredErrors>
 </worksheet>
 </file>